--- a/artfynd/A 65258-2019 artfynd.xlsx
+++ b/artfynd/A 65258-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65258-2019 artfynd.xlsx
+++ b/artfynd/A 65258-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16964517</v>
+        <v>126576788</v>
       </c>
       <c r="B2" t="n">
-        <v>95516</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1895</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strandlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodiella inundata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Holub</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bullerupsberget, SV om, Vrm</t>
+          <t>NV Bullerupsberget, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452368.1200431021</v>
+        <v>452245</v>
       </c>
       <c r="R2" t="n">
-        <v>6648309.246805411</v>
+        <v>6649213</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,34 +750,14 @@
           <t>Rämmen</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>S-Fil-0089</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3 grupper. Vid koordinat 3 m2; 6651242 - 1407334, 2 m2; 6651192 - 1407393, 2 m2.</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,26 +766,168 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsbilvägdike, fuktigt</t>
+          <t>Mindre gransumpskog hänsynskrävande med gammal gran.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16964517</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95516</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1895</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Strandlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodiella inundata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Holub</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bullerupsberget, SV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>452368.1200431021</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6648309.246805411</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rämmen</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>S-Fil-0089</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-06-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-06-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3 grupper. Vid koordinat 3 m2; 6651242 - 1407334, 2 m2; 6651192 - 1407393, 2 m2.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skogsbilvägdike, fuktigt</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 65258-2019 artfynd.xlsx
+++ b/artfynd/A 65258-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126576788</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
